--- a/Models/Свиньи/results/Свиньи - Результаты прогнозов Prophet.xlsx
+++ b/Models/Свиньи/results/Свиньи - Результаты прогнозов Prophet.xlsx
@@ -478,31 +478,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>154.54</v>
+        <v>63.75</v>
       </c>
       <c r="E2" t="n">
-        <v>131.51</v>
+        <v>56.52</v>
       </c>
       <c r="F2" t="n">
-        <v>32.03</v>
+        <v>10.84</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>[479.22, 585.19, 733.46]</t>
+          <t>[506.29, 540.82, 593.32]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[314.19, 565.5, 523.64]</t>
+          <t>[553.23, 566.96, 496.85]</t>
         </is>
       </c>
     </row>
@@ -514,31 +514,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>100.9</v>
+        <v>154.64</v>
       </c>
       <c r="E3" t="n">
-        <v>74.97</v>
+        <v>123.33</v>
       </c>
       <c r="F3" t="n">
-        <v>14.37</v>
+        <v>24.94</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>[563.34, 688.53, 572.99]</t>
+          <t>[547.69, 601.94, 734.21]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[565.5, 523.64, 515.15]</t>
+          <t>[566.96, 496.85, 488.59]</t>
         </is>
       </c>
     </row>
@@ -550,31 +550,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>122.43</v>
+        <v>442.12</v>
       </c>
       <c r="E4" t="n">
-        <v>113.86</v>
+        <v>352.84</v>
       </c>
       <c r="F4" t="n">
-        <v>27.46</v>
+        <v>72.98</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>[683.47, 567.91, 438.94]</t>
+          <t>[596.11, 726.91, 1201.0]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[523.64, 515.15, 309.94]</t>
+          <t>[496.85, 488.59, 480.05]</t>
         </is>
       </c>
     </row>
@@ -586,31 +586,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>260.17</v>
+        <v>418.36</v>
       </c>
       <c r="E5" t="n">
-        <v>196.69</v>
+        <v>320.44</v>
       </c>
       <c r="F5" t="n">
-        <v>33.26</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>[555.04, 426.72, 1230.77]</t>
+          <t>[708.9, 1168.36, 316.42]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[515.15, 309.94, 797.36]</t>
+          <t>[488.59, 480.05, 263.72]</t>
         </is>
       </c>
     </row>
@@ -622,31 +622,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>273.16</v>
+        <v>364.46</v>
       </c>
       <c r="E6" t="n">
-        <v>241.4</v>
+        <v>222.68</v>
       </c>
       <c r="F6" t="n">
-        <v>36.26</v>
+        <v>48.43</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>[420.75, 1212.34, 1143.69]</t>
+          <t>[1110.38, 297.84, 344.38]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[309.94, 797.36, 945.29]</t>
+          <t>[480.05, 263.72, 340.79]</t>
         </is>
       </c>
     </row>
@@ -658,31 +658,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>229.28</v>
+        <v>44.28</v>
       </c>
       <c r="E7" t="n">
-        <v>174.96</v>
+        <v>35.97</v>
       </c>
       <c r="F7" t="n">
-        <v>21.11</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>[1165.37, 1094.36, 545.44]</t>
+          <t>[270.76, 309.64, 377.55]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[797.36, 945.29, 553.23]</t>
+          <t>[263.72, 340.79, 447.27]</t>
         </is>
       </c>
     </row>
@@ -694,31 +694,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>64.41</v>
+        <v>100.24</v>
       </c>
       <c r="E8" t="n">
-        <v>49.24</v>
+        <v>84.67</v>
       </c>
       <c r="F8" t="n">
-        <v>6.23</v>
+        <v>19.1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>[1051.81, 521.41, 557.58]</t>
+          <t>[311.9, 379.28, 310.32]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[945.29, 553.23, 566.96]</t>
+          <t>[340.79, 447.27, 467.44]</t>
         </is>
       </c>
     </row>
@@ -730,31 +730,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>63.75</v>
+        <v>111.35</v>
       </c>
       <c r="E9" t="n">
-        <v>56.52</v>
+        <v>104.09</v>
       </c>
       <c r="F9" t="n">
-        <v>10.84</v>
+        <v>25.56</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>[506.29, 540.82, 593.32]</t>
+          <t>[376.23, 307.76, 224.58]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[553.23, 566.96, 496.85]</t>
+          <t>[447.27, 467.44, 306.14]</t>
         </is>
       </c>
     </row>
@@ -766,31 +766,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>154.64</v>
+        <v>105.12</v>
       </c>
       <c r="E10" t="n">
-        <v>123.33</v>
+        <v>94.5</v>
       </c>
       <c r="F10" t="n">
-        <v>24.94</v>
+        <v>22.1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>[547.69, 601.94, 734.21]</t>
+          <t>[310.54, 226.8, 646.96]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[566.96, 496.85, 488.59]</t>
+          <t>[467.44, 306.14, 694.22]</t>
         </is>
       </c>
     </row>
@@ -802,31 +802,31 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>442.12</v>
+        <v>98.72</v>
       </c>
       <c r="E11" t="n">
-        <v>352.84</v>
+        <v>76.5</v>
       </c>
       <c r="F11" t="n">
-        <v>72.98</v>
+        <v>13.99</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>[596.11, 726.91, 1201.0]</t>
+          <t>[240.44, 688.18, 646.0]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[496.85, 488.59, 480.05]</t>
+          <t>[306.14, 694.22, 803.75]</t>
         </is>
       </c>
     </row>
@@ -838,31 +838,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>67.45</v>
+        <v>39.15</v>
       </c>
       <c r="E12" t="n">
-        <v>59.66</v>
+        <v>32.28</v>
       </c>
       <c r="F12" t="n">
-        <v>66.25</v>
+        <v>61.49</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>[24.7, 24.54, 29.08]</t>
+          <t>[11.47, 21.65, 22.78]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[60.6, 63.5, 133.2]</t>
+          <t>[7.6, 56.7, 80.7]</t>
         </is>
       </c>
     </row>
@@ -874,31 +874,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>74.34999999999999</v>
+        <v>40.95</v>
       </c>
       <c r="E13" t="n">
-        <v>69.59</v>
+        <v>35.81</v>
       </c>
       <c r="F13" t="n">
-        <v>68.76000000000001</v>
+        <v>60.68</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>[27.24, 33.04, 25.44]</t>
+          <t>[20.01, 21.02, 14.44]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[63.5, 133.2, 97.8]</t>
+          <t>[56.7, 80.7, 25.5]</t>
         </is>
       </c>
     </row>
@@ -910,31 +910,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>69.08</v>
+        <v>33.86</v>
       </c>
       <c r="E14" t="n">
-        <v>57.85</v>
+        <v>23.78</v>
       </c>
       <c r="F14" t="n">
-        <v>67.88</v>
+        <v>42.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>[36.34, 27.88, 18.18]</t>
+          <t>[22.98, 15.84, 24.58]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[133.2, 97.8, 11.4]</t>
+          <t>[80.7, 25.5, 20.6]</t>
         </is>
       </c>
     </row>
@@ -946,31 +946,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>66.7</v>
+        <v>24.16</v>
       </c>
       <c r="E15" t="n">
-        <v>56.41</v>
+        <v>18.21</v>
       </c>
       <c r="F15" t="n">
-        <v>72.05</v>
+        <v>42.46</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>[30.48, 19.79, 33.38]</t>
+          <t>[16.8, 25.95, 19.73]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[97.8, 11.4, 126.9]</t>
+          <t>[25.5, 20.6, 60.3]</t>
         </is>
       </c>
     </row>
@@ -982,31 +982,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>53.82</v>
+        <v>32.73</v>
       </c>
       <c r="E16" t="n">
-        <v>40.12</v>
+        <v>28.62</v>
       </c>
       <c r="F16" t="n">
-        <v>69.36</v>
+        <v>54.29</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>[21.59, 36.35, 21.87]</t>
+          <t>[26.79, 20.31, 20.0]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[11.4, 126.9, 41.5]</t>
+          <t>[20.6, 60.3, 59.7]</t>
         </is>
       </c>
     </row>
@@ -1018,31 +1018,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>55.44</v>
+        <v>68</v>
       </c>
       <c r="E17" t="n">
-        <v>39.02</v>
+        <v>60.97</v>
       </c>
       <c r="F17" t="n">
-        <v>51.25</v>
+        <v>70.34</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>[33.29, 20.22, 9.78]</t>
+          <t>[20.46, 20.18, 27.95]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[126.9, 41.5, 7.6]</t>
+          <t>[60.3, 59.7, 131.5]</t>
         </is>
       </c>
     </row>
@@ -1054,31 +1054,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23.18</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>19.12</v>
+        <v>72.38</v>
       </c>
       <c r="F18" t="n">
-        <v>51.12</v>
+        <v>73.53</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>[23.34, 11.15, 21.07]</t>
+          <t>[20.58, 28.99, 22.41]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[41.5, 7.6, 56.7]</t>
+          <t>[59.7, 131.5, 97.9]</t>
         </is>
       </c>
     </row>
@@ -1090,31 +1090,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39.15</v>
+        <v>71.25</v>
       </c>
       <c r="E19" t="n">
-        <v>32.28</v>
+        <v>58.62</v>
       </c>
       <c r="F19" t="n">
-        <v>61.49</v>
+        <v>62.41</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>[11.47, 21.65, 22.78]</t>
+          <t>[32.03, 24.93, 12.61]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[7.6, 56.7, 80.7]</t>
+          <t>[131.5, 97.9, 9.2]</t>
         </is>
       </c>
     </row>
@@ -1126,31 +1126,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>40.95</v>
+        <v>69.92</v>
       </c>
       <c r="E20" t="n">
-        <v>35.81</v>
+        <v>57.76</v>
       </c>
       <c r="F20" t="n">
-        <v>60.68</v>
+        <v>64.78</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>[20.01, 21.02, 14.44]</t>
+          <t>[26.33, 13.31, 29.89]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[56.7, 80.7, 25.5]</t>
+          <t>[97.9, 9.2, 127.5]</t>
         </is>
       </c>
     </row>
@@ -1162,31 +1162,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>33.86</v>
+        <v>55.86</v>
       </c>
       <c r="E21" t="n">
-        <v>23.78</v>
+        <v>40.68</v>
       </c>
       <c r="F21" t="n">
-        <v>42.9</v>
+        <v>63.08</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>[22.98, 15.84, 24.58]</t>
+          <t>[14.8, 33.56, 18.6]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[80.7, 25.5, 20.6]</t>
+          <t>[9.2, 127.5, 41.1]</t>
         </is>
       </c>
     </row>
@@ -1198,31 +1198,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>118.59</v>
+        <v>207.3</v>
       </c>
       <c r="E22" t="n">
-        <v>102.42</v>
+        <v>188.65</v>
       </c>
       <c r="F22" t="n">
-        <v>132.17</v>
+        <v>54.32</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>[155.08, 210.51, 255.84]</t>
+          <t>[138.96, 162.74, 126.31]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[68.43, 172.15, 73.6]</t>
+          <t>[236.84, 466.77, 290.34]</t>
         </is>
       </c>
     </row>
@@ -1234,31 +1234,31 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>104.76</v>
+        <v>209</v>
       </c>
       <c r="E23" t="n">
-        <v>85.81999999999999</v>
+        <v>196.69</v>
       </c>
       <c r="F23" t="n">
-        <v>99.02</v>
+        <v>546.95</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>[206.46, 243.68, 168.38]</t>
+          <t>[170.8, 133.34, 146.1]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[172.15, 73.6, 115.3]</t>
+          <t>[466.77, 290.34, 9.0]</t>
         </is>
       </c>
     </row>
@@ -1270,31 +1270,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>123.78</v>
+        <v>116.63</v>
       </c>
       <c r="E24" t="n">
-        <v>114.59</v>
+        <v>105.33</v>
       </c>
       <c r="F24" t="n">
-        <v>130.36</v>
+        <v>542.72</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>[242.74, 170.14, 225.14]</t>
+          <t>[149.01, 149.17, 121.72]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[73.6, 115.3, 105.35]</t>
+          <t>[290.34, 9.0, 156.2]</t>
         </is>
       </c>
     </row>
@@ -1306,31 +1306,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>146.54</v>
+        <v>95.77</v>
       </c>
       <c r="E25" t="n">
-        <v>128.57</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>123.51</v>
+        <v>608.67</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>[166.79, 218.02, 322.73]</t>
+          <t>[162.01, 124.31, 108.26]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[115.3, 105.35, 101.19]</t>
+          <t>[9.0, 156.2, 52.7]</t>
         </is>
       </c>
     </row>
@@ -1342,31 +1342,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>161.53</v>
+        <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>147.27</v>
+        <v>27.56</v>
       </c>
       <c r="F26" t="n">
-        <v>143.81</v>
+        <v>34.09</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>[227.88, 339.23, 182.96]</t>
+          <t>[118.25, 89.95, 110.19]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[105.35, 101.19, 101.72]</t>
+          <t>[156.2, 52.7, 102.7]</t>
         </is>
       </c>
     </row>
@@ -1378,31 +1378,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>124.44</v>
+        <v>30.89</v>
       </c>
       <c r="E27" t="n">
-        <v>109.18</v>
+        <v>26.29</v>
       </c>
       <c r="F27" t="n">
-        <v>92.36</v>
+        <v>29.42</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>[293.23, 155.37, 154.99]</t>
+          <t>[83.38, 107.31, 127.0]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[101.19, 101.72, 236.84]</t>
+          <t>[52.7, 102.7, 170.6]</t>
         </is>
       </c>
     </row>
@@ -1414,31 +1414,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>187</v>
+        <v>45.84</v>
       </c>
       <c r="E28" t="n">
-        <v>150.79</v>
+        <v>38.15</v>
       </c>
       <c r="F28" t="n">
-        <v>52.24</v>
+        <v>71.53</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>[153.77, 141.71, 161.57]</t>
+          <t>[106.83, 125.46, 100.58]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[101.72, 236.84, 466.77]</t>
+          <t>[102.7, 170.6, 35.4]</t>
         </is>
       </c>
     </row>
@@ -1450,31 +1450,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>207.3</v>
+        <v>73</v>
       </c>
       <c r="E29" t="n">
-        <v>188.65</v>
+        <v>69.67</v>
       </c>
       <c r="F29" t="n">
-        <v>54.32</v>
+        <v>348.21</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>[138.96, 162.74, 126.31]</t>
+          <t>[124.65, 99.86, 110.4]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[236.84, 466.77, 290.34]</t>
+          <t>[170.6, 35.4, 11.8]</t>
         </is>
       </c>
     </row>
@@ -1486,31 +1486,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>209</v>
+        <v>94.48999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>196.69</v>
+        <v>92.48999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>546.95</v>
+        <v>443.03</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>[170.8, 133.34, 146.1]</t>
+          <t>[101.29, 112.12, 149.27]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[466.77, 290.34, 9.0]</t>
+          <t>[35.4, 11.8, 38.0]</t>
         </is>
       </c>
     </row>
@@ -1522,31 +1522,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>116.63</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>105.33</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>542.72</v>
+        <v>401.46</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>[149.01, 149.17, 121.72]</t>
+          <t>[102.62, 136.29, 74.26]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[290.34, 9.0, 156.2]</t>
+          <t>[11.8, 38.0, 26.9]</t>
         </is>
       </c>
     </row>
@@ -1558,19 +1558,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3.73</v>
+        <v>2.19</v>
       </c>
       <c r="E32" t="n">
-        <v>2.38</v>
+        <v>1.27</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[0.71, 6.43, 0.0]</t>
+          <t>[3.8, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1596,19 +1596,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[6.43, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1748,19 +1748,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 3.8]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1786,19 +1786,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[0.0, 3.8, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1824,19 +1824,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>[0.0, -0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>[0.0, 0.0, 0.0]</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>[3.8, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1938,31 +1938,31 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>76.09999999999999</v>
+        <v>132.25</v>
       </c>
       <c r="E42" t="n">
-        <v>70.81999999999999</v>
+        <v>123.92</v>
       </c>
       <c r="F42" t="n">
-        <v>19.1</v>
+        <v>30.66</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>[274.73, 273.35, 316.19]</t>
+          <t>[288.6, 264.86, 241.86]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[325.4, 324.95, 426.38]</t>
+          <t>[463.17, 399.19, 304.73]</t>
         </is>
       </c>
     </row>
@@ -1974,31 +1974,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>94.22</v>
+        <v>105.62</v>
       </c>
       <c r="E43" t="n">
-        <v>90.12</v>
+        <v>100.44</v>
       </c>
       <c r="F43" t="n">
-        <v>22.79</v>
+        <v>29.48</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>[273.64, 318.0, 296.66]</t>
+          <t>[274.18, 250.46, 432.44]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[324.95, 426.38, 407.34]</t>
+          <t>[399.19, 304.73, 310.4]</t>
         </is>
       </c>
     </row>
@@ -2010,31 +2010,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>98.01000000000001</v>
+        <v>114.94</v>
       </c>
       <c r="E44" t="n">
-        <v>97.98</v>
+        <v>106.55</v>
       </c>
       <c r="F44" t="n">
-        <v>24.45</v>
+        <v>28.24</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>[329.2, 306.12, 276.06]</t>
+          <t>[258.22, 437.82, 367.48]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[426.38, 407.34, 371.6]</t>
+          <t>[304.73, 310.4, 513.21]</t>
         </is>
       </c>
     </row>
@@ -2046,31 +2046,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>146.94</v>
+        <v>118.75</v>
       </c>
       <c r="E45" t="n">
-        <v>134.96</v>
+        <v>115.46</v>
       </c>
       <c r="F45" t="n">
-        <v>27.85</v>
+        <v>30.47</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>[310.16, 280.95, 397.86]</t>
+          <t>[442.69, 375.45, 271.36]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[407.34, 371.6, 614.91]</t>
+          <t>[310.4, 513.21, 347.69]</t>
         </is>
       </c>
     </row>
@@ -2082,31 +2082,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>148.05</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>138.69</v>
+        <v>80.62</v>
       </c>
       <c r="F46" t="n">
-        <v>29.96</v>
+        <v>18.74</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>[285.86, 405.89, 248.44]</t>
+          <t>[363.48, 264.77, 279.44]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[371.6, 614.91, 369.74]</t>
+          <t>[513.21, 347.69, 288.64]</t>
         </is>
       </c>
     </row>
@@ -2118,31 +2118,31 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>172.44</v>
+        <v>51.66</v>
       </c>
       <c r="E47" t="n">
-        <v>168.06</v>
+        <v>41.48</v>
       </c>
       <c r="F47" t="n">
-        <v>34.84</v>
+        <v>13.18</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>[417.51, 256.2, 269.92]</t>
+          <t>[271.14, 287.07, 319.25]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[614.91, 369.74, 463.17]</t>
+          <t>[347.69, 288.64, 272.95]</t>
         </is>
       </c>
     </row>
@@ -2154,31 +2154,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>147.02</v>
+        <v>37.32</v>
       </c>
       <c r="E48" t="n">
-        <v>143.52</v>
+        <v>30.85</v>
       </c>
       <c r="F48" t="n">
-        <v>34.54</v>
+        <v>11.25</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>[264.67, 280.02, 256.83]</t>
+          <t>[291.28, 325.98, 311.7]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[369.74, 463.17, 399.19]</t>
+          <t>[288.64, 272.95, 274.81]</t>
         </is>
       </c>
     </row>
@@ -2190,31 +2190,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>132.25</v>
+        <v>36.18</v>
       </c>
       <c r="E49" t="n">
-        <v>123.92</v>
+        <v>30.88</v>
       </c>
       <c r="F49" t="n">
-        <v>30.66</v>
+        <v>11.25</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>[288.6, 264.86, 241.86]</t>
+          <t>[324.4, 310.09, 281.2]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[463.17, 399.19, 304.73]</t>
+          <t>[272.95, 274.81, 287.1]</t>
         </is>
       </c>
     </row>
@@ -2226,31 +2226,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>105.62</v>
+        <v>31.69</v>
       </c>
       <c r="E50" t="n">
-        <v>100.44</v>
+        <v>28.31</v>
       </c>
       <c r="F50" t="n">
-        <v>29.48</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>[274.18, 250.46, 432.44]</t>
+          <t>[306.06, 277.51, 412.76]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[399.19, 304.73, 310.4]</t>
+          <t>[274.81, 287.1, 368.67]</t>
         </is>
       </c>
     </row>
@@ -2262,31 +2262,31 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>114.94</v>
+        <v>29.23</v>
       </c>
       <c r="E51" t="n">
-        <v>106.55</v>
+        <v>26.37</v>
       </c>
       <c r="F51" t="n">
-        <v>28.24</v>
+        <v>8.32</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>[258.22, 437.82, 367.48]</t>
+          <t>[276.1, 410.51, 242.66]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[304.73, 310.4, 513.21]</t>
+          <t>[287.1, 368.67, 268.94]</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2336,19 +2336,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2357,12 +2357,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 1.4]</t>
         </is>
       </c>
     </row>
@@ -2374,19 +2374,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2395,12 +2395,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 1.4, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2412,19 +2412,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[1.4, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2526,12 +2526,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, -0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2602,19 +2602,19 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2623,12 +2623,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 1.4]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2640,19 +2640,19 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="E61" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2661,12 +2661,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, -0.0]</t>
+          <t>[0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[0.0, 1.4, 0.0]</t>
+          <t>[0.0, 0.0, 2.2]</t>
         </is>
       </c>
     </row>
@@ -2678,19 +2678,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E62" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.1, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2716,19 +2716,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.1, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.1]</t>
         </is>
       </c>
     </row>
@@ -2792,19 +2792,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.1, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2830,19 +2830,19 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="E66" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.1, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2906,19 +2906,19 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2944,19 +2944,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[0.0, 0.1, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -2982,19 +2982,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[0.1, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3020,19 +3020,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.1]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -3058,31 +3058,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.51</v>
+        <v>3.56</v>
       </c>
       <c r="E72" t="n">
-        <v>1.37</v>
+        <v>2.98</v>
       </c>
       <c r="F72" t="n">
-        <v>45.71</v>
+        <v>63.77</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[1.57, 1.2, 1.53]</t>
+          <t>[1.73, 2.82, 5.26]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[3.3, 3.1, 2.0]</t>
+          <t>[0.9, 5.4, 10.8]</t>
         </is>
       </c>
     </row>
@@ -3094,31 +3094,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.31</v>
+        <v>3.86</v>
       </c>
       <c r="E73" t="n">
-        <v>1.14</v>
+        <v>3.62</v>
       </c>
       <c r="F73" t="n">
-        <v>43.28</v>
+        <v>47.65</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[1.18, 1.64, 1.15]</t>
+          <t>[2.88, 5.31, 3.44]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[3.1, 2.0, 2.3]</t>
+          <t>[5.4, 10.8, 6.3]</t>
         </is>
       </c>
     </row>
@@ -3130,31 +3130,31 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.62</v>
+        <v>10.12</v>
       </c>
       <c r="E74" t="n">
-        <v>0.45</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F74" t="n">
-        <v>22.06</v>
+        <v>59.65</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[1.84, 1.26, 1.24]</t>
+          <t>[5.19, 3.4, 3.85]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[2.0, 2.3, 1.1]</t>
+          <t>[10.8, 6.3, 20.2]</t>
         </is>
       </c>
     </row>
@@ -3166,31 +3166,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.67</v>
+        <v>9.67</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5600000000000001</v>
+        <v>7</v>
       </c>
       <c r="F75" t="n">
-        <v>30.05</v>
+        <v>59.18</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[1.25, 1.24, 1.02]</t>
+          <t>[3.3, 3.8, 1.69]</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[2.3, 1.1, 1.5]</t>
+          <t>[6.3, 20.2, 3.3]</t>
         </is>
       </c>
     </row>
@@ -3202,31 +3202,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.3</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E76" t="n">
-        <v>0.25</v>
+        <v>6.57</v>
       </c>
       <c r="F76" t="n">
-        <v>17.96</v>
+        <v>60.65</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[1.21, 1.01, 1.15]</t>
+          <t>[3.7, 1.68, 1.51]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[1.1, 1.5, 1.3]</t>
+          <t>[20.2, 3.3, 3.1]</t>
         </is>
       </c>
     </row>
@@ -3238,31 +3238,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.57</v>
+        <v>1.48</v>
       </c>
       <c r="E77" t="n">
-        <v>0.49</v>
+        <v>1.43</v>
       </c>
       <c r="F77" t="n">
-        <v>45.8</v>
+        <v>79.39</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[1.02, 1.16, 1.75]</t>
+          <t>[1.57, 1.46, 1.63]</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[1.5, 1.3, 0.9]</t>
+          <t>[3.3, 3.1, 0.7]</t>
         </is>
       </c>
     </row>
@@ -3274,31 +3274,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="E78" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="F78" t="n">
-        <v>50.92</v>
+        <v>78.94</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[1.14, 1.74, 2.83]</t>
+          <t>[1.41, 1.65, 1.46]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[1.3, 0.9, 5.4]</t>
+          <t>[3.1, 0.7, 1.0]</t>
         </is>
       </c>
     </row>
@@ -3310,31 +3310,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>3.56</v>
+        <v>0.63</v>
       </c>
       <c r="E79" t="n">
-        <v>2.98</v>
+        <v>0.54</v>
       </c>
       <c r="F79" t="n">
-        <v>63.77</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[1.73, 2.82, 5.26]</t>
+          <t>[1.67, 1.49, 0.95]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>[0.9, 5.4, 10.8]</t>
+          <t>[0.7, 1.0, 1.1]</t>
         </is>
       </c>
     </row>
@@ -3346,31 +3346,31 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>3.86</v>
+        <v>0.33</v>
       </c>
       <c r="E80" t="n">
-        <v>3.62</v>
+        <v>0.31</v>
       </c>
       <c r="F80" t="n">
-        <v>47.65</v>
+        <v>31.94</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[2.88, 5.31, 3.44]</t>
+          <t>[1.46, 0.93, 1.21]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>[5.4, 10.8, 6.3]</t>
+          <t>[1.0, 1.1, 0.9]</t>
         </is>
       </c>
     </row>
@@ -3382,31 +3382,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.12</v>
+        <v>0.32</v>
       </c>
       <c r="E81" t="n">
-        <v>8.289999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="F81" t="n">
-        <v>59.65</v>
+        <v>34.54</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[5.19, 3.4, 3.85]</t>
+          <t>[0.91, 1.19, 1.24]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>[10.8, 6.3, 20.2]</t>
+          <t>[1.1, 0.9, 0.8]</t>
         </is>
       </c>
     </row>
@@ -3418,31 +3418,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6.9</v>
+        <v>10.73</v>
       </c>
       <c r="E82" t="n">
-        <v>5.73</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F82" t="n">
-        <v>15.61</v>
+        <v>36.77</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[37.12, 28.53, 29.54]</t>
+          <t>[22.33, 35.26, 32.55]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>[48.0, 30.2, 24.9]</t>
+          <t>[13.9, 51.0, 27.4]</t>
         </is>
       </c>
     </row>
@@ -3454,31 +3454,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3.67</v>
+        <v>16.17</v>
       </c>
       <c r="E83" t="n">
-        <v>2.92</v>
+        <v>14.21</v>
       </c>
       <c r="F83" t="n">
-        <v>11.12</v>
+        <v>29.73</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[29.25, 30.92, 31.18]</t>
+          <t>[34.46, 31.21, 29.72]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>[30.2, 24.9, 29.4]</t>
+          <t>[51.0, 27.4, 52.0]</t>
         </is>
       </c>
     </row>
@@ -3490,31 +3490,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>7.43</v>
+        <v>12.51</v>
       </c>
       <c r="E84" t="n">
-        <v>6.7</v>
+        <v>10.58</v>
       </c>
       <c r="F84" t="n">
-        <v>38.32</v>
+        <v>27.23</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[32.37, 31.82, 23.5]</t>
+          <t>[33.46, 31.98, 21.24]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>[24.9, 29.4, 13.3]</t>
+          <t>[27.4, 52.0, 26.9]</t>
         </is>
       </c>
     </row>
@@ -3526,31 +3526,31 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>23.72</v>
+        <v>18.39</v>
       </c>
       <c r="E85" t="n">
-        <v>16.36</v>
+        <v>16.81</v>
       </c>
       <c r="F85" t="n">
-        <v>37.95</v>
+        <v>37.31</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[28.74, 21.44, 39.64]</t>
+          <t>[31.05, 20.56, 24.97]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>[29.4, 13.3, 79.9]</t>
+          <t>[52.0, 26.9, 48.1]</t>
         </is>
       </c>
     </row>
@@ -3562,31 +3562,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>26.77</v>
+        <v>15.13</v>
       </c>
       <c r="E86" t="n">
-        <v>18.78</v>
+        <v>13.48</v>
       </c>
       <c r="F86" t="n">
-        <v>44.26</v>
+        <v>36.17</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[21.68, 34.36, 21.42]</t>
+          <t>[21.37, 25.8, 17.69]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>[13.3, 79.9, 19.0]</t>
+          <t>[26.9, 48.1, 30.3]</t>
         </is>
       </c>
     </row>
@@ -3598,31 +3598,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>26.58</v>
+        <v>15.02</v>
       </c>
       <c r="E87" t="n">
-        <v>18.24</v>
+        <v>13.35</v>
       </c>
       <c r="F87" t="n">
-        <v>39.79</v>
+        <v>36.26</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[34.47, 21.24, 20.95]</t>
+          <t>[26.06, 17.5, 19.91]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>[79.9, 19.0, 13.9]</t>
+          <t>[48.1, 30.3, 25.1]</t>
         </is>
       </c>
     </row>
@@ -3634,31 +3634,31 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>9.93</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E88" t="n">
-        <v>9.390000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="F88" t="n">
-        <v>40.28</v>
+        <v>28.21</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[24.63, 22.89, 37.46]</t>
+          <t>[18.94, 20.53, 21.11]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>[19.0, 13.9, 51.0]</t>
+          <t>[30.3, 25.1, 29.7]</t>
         </is>
       </c>
     </row>
@@ -3670,31 +3670,31 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.73</v>
+        <v>4.93</v>
       </c>
       <c r="E89" t="n">
-        <v>9.779999999999999</v>
+        <v>4.52</v>
       </c>
       <c r="F89" t="n">
-        <v>36.77</v>
+        <v>19.94</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[22.33, 35.26, 32.55]</t>
+          <t>[21.73, 22.4, 16.2]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>[13.9, 51.0, 27.4]</t>
+          <t>[25.1, 29.7, 13.3]</t>
         </is>
       </c>
     </row>
@@ -3706,31 +3706,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>16.17</v>
+        <v>27.93</v>
       </c>
       <c r="E90" t="n">
-        <v>14.21</v>
+        <v>19.33</v>
       </c>
       <c r="F90" t="n">
-        <v>29.73</v>
+        <v>34.13</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[34.46, 31.21, 29.72]</t>
+          <t>[21.9, 15.81, 35.52]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>[51.0, 27.4, 52.0]</t>
+          <t>[29.7, 13.3, 83.2]</t>
         </is>
       </c>
     </row>
@@ -3742,31 +3742,31 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.51</v>
+        <v>27.72</v>
       </c>
       <c r="E91" t="n">
-        <v>10.58</v>
+        <v>20.88</v>
       </c>
       <c r="F91" t="n">
-        <v>27.23</v>
+        <v>116.14</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[33.46, 31.98, 21.24]</t>
+          <t>[16.54, 37.23, 18.44]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>[27.4, 52.0, 26.9]</t>
+          <t>[13.3, 83.2, 5.0]</t>
         </is>
       </c>
     </row>
@@ -3778,31 +3778,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>28.6</v>
+        <v>29.12</v>
       </c>
       <c r="E92" t="n">
-        <v>23.03</v>
+        <v>27.89</v>
       </c>
       <c r="F92" t="n">
-        <v>13.89</v>
+        <v>16.26</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[99.8, 170.63, 210.78]</t>
+          <t>[144.2, 149.09, 135.15]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>[143.6, 172.9, 233.8]</t>
+          <t>[167.7, 169.6, 174.8]</t>
         </is>
       </c>
     </row>
@@ -3814,31 +3814,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>17.19</v>
+        <v>27.53</v>
       </c>
       <c r="E93" t="n">
-        <v>14.44</v>
+        <v>25.31</v>
       </c>
       <c r="F93" t="n">
-        <v>7.02</v>
+        <v>14.93</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[171.24, 215.85, 167.1]</t>
+          <t>[147.46, 134.92, 141.98]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>[172.9, 233.8, 190.8]</t>
+          <t>[169.6, 174.8, 155.9]</t>
         </is>
       </c>
     </row>
@@ -3850,31 +3850,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>26.27</v>
+        <v>29.73</v>
       </c>
       <c r="E94" t="n">
-        <v>25.28</v>
+        <v>27.84</v>
       </c>
       <c r="F94" t="n">
-        <v>11.49</v>
+        <v>16.45</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[212.72, 171.35, 195.98]</t>
+          <t>[135.27, 141.7, 198.69]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>[233.8, 190.8, 231.3]</t>
+          <t>[174.8, 155.9, 168.9]</t>
         </is>
       </c>
     </row>
@@ -3886,31 +3886,31 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>38.3</v>
+        <v>27.71</v>
       </c>
       <c r="E95" t="n">
-        <v>36.28</v>
+        <v>26.29</v>
       </c>
       <c r="F95" t="n">
-        <v>20.74</v>
+        <v>17.31</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[169.36, 195.37, 196.6]</t>
+          <t>[142.01, 201.36, 104.1]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>[190.8, 231.3, 145.13]</t>
+          <t>[155.9, 168.9, 136.6]</t>
         </is>
       </c>
     </row>
@@ -3922,31 +3922,31 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>36.63</v>
+        <v>26.75</v>
       </c>
       <c r="E96" t="n">
-        <v>29.29</v>
+        <v>22.9</v>
       </c>
       <c r="F96" t="n">
-        <v>17.21</v>
+        <v>15.07</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[196.59, 198.24, 165.24]</t>
+          <t>[201.94, 104.28, 171.95]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>[231.3, 145.13, 165.3]</t>
+          <t>[168.9, 136.6, 168.6]</t>
         </is>
       </c>
     </row>
@@ -3958,31 +3958,31 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>33.86</v>
+        <v>23.75</v>
       </c>
       <c r="E97" t="n">
-        <v>26.17</v>
+        <v>19.62</v>
       </c>
       <c r="F97" t="n">
-        <v>17.31</v>
+        <v>11.81</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[199.87, 168.24, 146.86]</t>
+          <t>[103.73, 169.88, 208.1]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>[145.13, 165.3, 167.7]</t>
+          <t>[136.6, 168.6, 232.8]</t>
         </is>
       </c>
     </row>
@@ -3994,31 +3994,31 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>18.31</v>
+        <v>28.04</v>
       </c>
       <c r="E98" t="n">
-        <v>17.03</v>
+        <v>22.77</v>
       </c>
       <c r="F98" t="n">
-        <v>10.13</v>
+        <v>10.54</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[173.09, 144.15, 149.86]</t>
+          <t>[172.28, 211.85, 170.13]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>[165.3, 167.7, 169.6]</t>
+          <t>[168.6, 232.8, 213.8]</t>
         </is>
       </c>
     </row>
@@ -4030,31 +4030,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>29.12</v>
+        <v>32.35</v>
       </c>
       <c r="E99" t="n">
-        <v>27.89</v>
+        <v>30.9</v>
       </c>
       <c r="F99" t="n">
-        <v>16.26</v>
+        <v>14</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[144.2, 149.09, 135.15]</t>
+          <t>[211.05, 169.67, 196.59]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>[167.7, 169.6, 174.8]</t>
+          <t>[232.8, 213.8, 223.4]</t>
         </is>
       </c>
     </row>
@@ -4066,31 +4066,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>27.53</v>
+        <v>30</v>
       </c>
       <c r="E100" t="n">
-        <v>25.31</v>
+        <v>25.59</v>
       </c>
       <c r="F100" t="n">
-        <v>14.93</v>
+        <v>11.95</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[147.46, 134.92, 141.98]</t>
+          <t>[169.79, 196.35, 185.81]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>[169.6, 174.8, 155.9]</t>
+          <t>[213.8, 223.4, 180.1]</t>
         </is>
       </c>
     </row>
@@ -4102,31 +4102,31 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>29.73</v>
+        <v>15.44</v>
       </c>
       <c r="E101" t="n">
-        <v>27.84</v>
+        <v>12.19</v>
       </c>
       <c r="F101" t="n">
-        <v>16.45</v>
+        <v>5.92</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[135.27, 141.7, 198.69]</t>
+          <t>[197.94, 187.3, 162.68]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>[174.8, 155.9, 168.9]</t>
+          <t>[223.4, 180.1, 166.6]</t>
         </is>
       </c>
     </row>
@@ -4138,31 +4138,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>115.21</v>
+        <v>10.9</v>
       </c>
       <c r="E102" t="n">
-        <v>100.55</v>
+        <v>7.35</v>
       </c>
       <c r="F102" t="n">
-        <v>13.84</v>
+        <v>0.92</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>[561.68, 591.98, 667.89]</t>
+          <t>[731.06, 780.85, 779.36]</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>[627.0, 771.9, 724.31]</t>
+          <t>[731.19, 799.44, 776.04]</t>
         </is>
       </c>
     </row>
@@ -4174,31 +4174,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>113.58</v>
+        <v>76</v>
       </c>
       <c r="E103" t="n">
-        <v>99.67</v>
+        <v>51.04</v>
       </c>
       <c r="F103" t="n">
-        <v>12.97</v>
+        <v>5.94</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>[596.97, 676.45, 715.51]</t>
+          <t>[783.09, 782.35, 741.21]</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>[771.9, 724.31, 791.73]</t>
+          <t>[799.44, 776.04, 871.68]</t>
         </is>
       </c>
     </row>
@@ -4210,31 +4210,31 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>32.19</v>
+        <v>90.31</v>
       </c>
       <c r="E104" t="n">
-        <v>27.19</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="F104" t="n">
-        <v>3.51</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>[703.71, 740.92, 789.72]</t>
+          <t>[784.15, 739.18, 1017.41]</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>[724.31, 791.73, 799.86]</t>
+          <t>[776.04, 871.68, 934.66]</t>
         </is>
       </c>
     </row>
@@ -4246,31 +4246,31 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>51.58</v>
+        <v>89.03</v>
       </c>
       <c r="E105" t="n">
-        <v>42.94</v>
+        <v>77.64</v>
       </c>
       <c r="F105" t="n">
-        <v>5.37</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>[744.45, 793.88, 728.8]</t>
+          <t>[739.37, 1009.58, 588.99]</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>[791.73, 799.86, 804.37]</t>
+          <t>[871.68, 934.66, 614.67]</t>
         </is>
       </c>
     </row>
@@ -4282,31 +4282,31 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>89.47</v>
+        <v>51.34</v>
       </c>
       <c r="E106" t="n">
-        <v>72.55</v>
+        <v>36.73</v>
       </c>
       <c r="F106" t="n">
-        <v>9.460000000000001</v>
+        <v>4.36</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>[793.55, 727.37, 611.2]</t>
+          <t>[1021.32, 595.12, 646.06]</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>[799.86, 804.37, 745.53]</t>
+          <t>[934.66, 614.67, 650.04]</t>
         </is>
       </c>
     </row>
@@ -4318,31 +4318,31 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>93.5</v>
+        <v>119.84</v>
       </c>
       <c r="E107" t="n">
-        <v>81.09999999999999</v>
+        <v>79.56</v>
       </c>
       <c r="F107" t="n">
-        <v>10.62</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>[719.41, 609.46, 708.93]</t>
+          <t>[591.13, 640.92, 673.27]</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>[804.37, 745.53, 731.19]</t>
+          <t>[614.67, 650.04, 879.3]</t>
         </is>
       </c>
     </row>
@@ -4354,31 +4354,31 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>80.98</v>
+        <v>233.67</v>
       </c>
       <c r="E108" t="n">
-        <v>61.72</v>
+        <v>185.3</v>
       </c>
       <c r="F108" t="n">
-        <v>8.18</v>
+        <v>18.94</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>[610.79, 717.11, 763.08]</t>
+          <t>[646.05, 679.13, 700.5]</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>[745.53, 731.19, 799.44]</t>
+          <t>[650.04, 879.3, 1052.23]</t>
         </is>
       </c>
     </row>
@@ -4390,31 +4390,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.9</v>
+        <v>342.63</v>
       </c>
       <c r="E109" t="n">
-        <v>7.35</v>
+        <v>329.05</v>
       </c>
       <c r="F109" t="n">
-        <v>0.92</v>
+        <v>31.03</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>[731.06, 780.85, 779.36]</t>
+          <t>[677.66, 698.34, 750.17]</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>[731.19, 799.44, 776.04]</t>
+          <t>[879.3, 1052.23, 1181.78]</t>
         </is>
       </c>
     </row>
@@ -4426,31 +4426,31 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>76</v>
+        <v>370.59</v>
       </c>
       <c r="E110" t="n">
-        <v>51.04</v>
+        <v>369.16</v>
       </c>
       <c r="F110" t="n">
-        <v>5.94</v>
+        <v>33.28</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>[783.09, 782.35, 741.21]</t>
+          <t>[714.04, 767.77, 732.08]</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>[799.44, 776.04, 871.68]</t>
+          <t>[1052.23, 1181.78, 1087.37]</t>
         </is>
       </c>
     </row>
@@ -4462,31 +4462,31 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>90.31</v>
+        <v>324.14</v>
       </c>
       <c r="E111" t="n">
-        <v>74.45999999999999</v>
+        <v>317.85</v>
       </c>
       <c r="F111" t="n">
-        <v>8.369999999999999</v>
+        <v>30.37</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>[784.15, 739.18, 1017.41]</t>
+          <t>[793.24, 756.84, 608.11]</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>[776.04, 871.68, 934.66]</t>
+          <t>[1181.78, 1087.37, 842.58]</t>
         </is>
       </c>
     </row>
@@ -4498,31 +4498,31 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>122.59</v>
+        <v>46.7</v>
       </c>
       <c r="E112" t="n">
-        <v>118.45</v>
+        <v>41.65</v>
       </c>
       <c r="F112" t="n">
-        <v>30.05</v>
+        <v>11.62</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>[622.39, 392.45, 88.76]</t>
+          <t>[312.12, 238.35, 364.56]</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>[767.11, 529.05, 162.8]</t>
+          <t>[332.33, 272.7, 434.95]</t>
         </is>
       </c>
     </row>
@@ -4534,31 +4534,31 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>90.26000000000001</v>
+        <v>54.98</v>
       </c>
       <c r="E113" t="n">
-        <v>80.62</v>
+        <v>52.97</v>
       </c>
       <c r="F113" t="n">
-        <v>41.13</v>
+        <v>13.07</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>[395.16, 90.32, 30.8]</t>
+          <t>[238.51, 364.87, 462.97]</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>[529.05, 162.8, 66.3]</t>
+          <t>[272.7, 434.95, 517.61]</t>
         </is>
       </c>
     </row>
@@ -4570,31 +4570,31 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>52.25</v>
+        <v>51.77</v>
       </c>
       <c r="E114" t="n">
-        <v>50.43</v>
+        <v>50.62</v>
       </c>
       <c r="F114" t="n">
-        <v>43.41</v>
+        <v>10.53</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>[95.13, 31.99, 84.26]</t>
+          <t>[369.85, 469.85, 567.18]</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>[162.8, 66.3, 133.58]</t>
+          <t>[434.95, 517.61, 528.19]</t>
         </is>
       </c>
     </row>
@@ -4606,31 +4606,31 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>37.86</v>
+        <v>206.06</v>
       </c>
       <c r="E115" t="n">
-        <v>37.42</v>
+        <v>146.83</v>
       </c>
       <c r="F115" t="n">
-        <v>34.68</v>
+        <v>19.8</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>[33.41, 87.99, 132.57]</t>
+          <t>[474.31, 574.11, 478.28]</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>[66.3, 133.58, 166.34]</t>
+          <t>[517.61, 528.19, 829.56]</t>
         </is>
       </c>
     </row>
@@ -4642,31 +4642,31 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>53.84</v>
+        <v>251.62</v>
       </c>
       <c r="E116" t="n">
-        <v>48.44</v>
+        <v>216.57</v>
       </c>
       <c r="F116" t="n">
-        <v>30.35</v>
+        <v>32.14</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>[93.07, 141.91, 94.19]</t>
+          <t>[572.74, 477.76, 302.38]</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>[133.58, 166.34, 174.56]</t>
+          <t>[528.19, 829.56, 555.74]</t>
         </is>
       </c>
     </row>
@@ -4678,31 +4678,31 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>50.5</v>
+        <v>262.83</v>
       </c>
       <c r="E117" t="n">
-        <v>44.17</v>
+        <v>245.59</v>
       </c>
       <c r="F117" t="n">
-        <v>22.03</v>
+        <v>51.15</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>[148.56, 97.76, 294.41]</t>
+          <t>[474.32, 300.73, 68.89]</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>[166.34, 174.56, 332.33]</t>
+          <t>[829.56, 555.74, 195.42]</t>
         </is>
       </c>
     </row>
@@ -4714,31 +4714,31 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>54.05</v>
+        <v>161.16</v>
       </c>
       <c r="E118" t="n">
-        <v>51.21</v>
+        <v>141.03</v>
       </c>
       <c r="F118" t="n">
-        <v>23.18</v>
+        <v>57.3</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>[99.77, 298.48, 227.71]</t>
+          <t>[311.46, 72.42, 30.06]</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>[174.56, 332.33, 272.7]</t>
+          <t>[555.74, 195.42, 85.87]</t>
         </is>
       </c>
     </row>
@@ -4750,31 +4750,31 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>46.7</v>
+        <v>80.52</v>
       </c>
       <c r="E119" t="n">
-        <v>41.65</v>
+        <v>73.78</v>
       </c>
       <c r="F119" t="n">
-        <v>11.62</v>
+        <v>55.11</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>[312.12, 238.35, 364.56]</t>
+          <t>[76.16, 31.75, 68.26]</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>[332.33, 272.7, 434.95]</t>
+          <t>[195.42, 85.87, 116.23]</t>
         </is>
       </c>
     </row>
@@ -4786,31 +4786,31 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>54.98</v>
+        <v>62.94</v>
       </c>
       <c r="E120" t="n">
-        <v>52.97</v>
+        <v>59.54</v>
       </c>
       <c r="F120" t="n">
-        <v>13.07</v>
+        <v>46.19</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[238.51, 364.87, 462.97]</t>
+          <t>[35.23, 76.03, 107.31]</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>[272.7, 434.95, 517.61]</t>
+          <t>[85.87, 116.23, 195.09]</t>
         </is>
       </c>
     </row>
@@ -4822,31 +4822,31 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>51.77</v>
+        <v>67.17</v>
       </c>
       <c r="E121" t="n">
-        <v>50.62</v>
+        <v>63.33</v>
       </c>
       <c r="F121" t="n">
-        <v>10.53</v>
+        <v>37.07</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>[369.85, 469.85, 567.18]</t>
+          <t>[84.27, 119.6, 100.86]</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>[434.95, 517.61, 528.19]</t>
+          <t>[116.23, 195.09, 183.42]</t>
         </is>
       </c>
     </row>
@@ -4858,31 +4858,31 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>33.13</v>
+        <v>1.67</v>
       </c>
       <c r="E122" t="n">
-        <v>24.37</v>
+        <v>1.46</v>
       </c>
       <c r="F122" t="n">
-        <v>178.61</v>
+        <v>27.05</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>[12.24, 12.48, 12.25]</t>
+          <t>[6.99, 5.24, 14.74]</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>[3.9, 68.6, 3.6]</t>
+          <t>[4.4, 4.6, 13.6]</t>
         </is>
       </c>
     </row>
@@ -4894,31 +4894,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>33.39</v>
+        <v>1.46</v>
       </c>
       <c r="E123" t="n">
-        <v>23.14</v>
+        <v>1.18</v>
       </c>
       <c r="F123" t="n">
-        <v>128.67</v>
+        <v>15.38</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>[11.44, 10.95, 9.93]</t>
+          <t>[5.22, 14.12, 5.9]</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>[68.6, 3.6, 5.0]</t>
+          <t>[4.6, 13.6, 8.3]</t>
         </is>
       </c>
     </row>
@@ -4930,31 +4930,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>7.47</v>
+        <v>1.43</v>
       </c>
       <c r="E124" t="n">
-        <v>6.96</v>
+        <v>1.23</v>
       </c>
       <c r="F124" t="n">
-        <v>166.58</v>
+        <v>16.05</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>[13.07, 13.24, 7.57]</t>
+          <t>[14.15, 6.06, 6.09]</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>[3.6, 5.0, 4.4]</t>
+          <t>[13.6, 8.3, 5.2]</t>
         </is>
       </c>
     </row>
@@ -4966,31 +4966,31 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>8.050000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="E125" t="n">
-        <v>7.43</v>
+        <v>2.42</v>
       </c>
       <c r="F125" t="n">
-        <v>215.93</v>
+        <v>54.65</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>[13.63, 7.58, 13.08]</t>
+          <t>[6.59, 6.5, 7.86]</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>[5.0, 4.4, 2.6]</t>
+          <t>[8.3, 5.2, 3.6]</t>
         </is>
       </c>
     </row>
@@ -5002,31 +5002,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6.92</v>
+        <v>36.4</v>
       </c>
       <c r="E126" t="n">
-        <v>6.37</v>
+        <v>22.84</v>
       </c>
       <c r="F126" t="n">
-        <v>215.86</v>
+        <v>78.70999999999999</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>[7.16, 11.86, 10.19]</t>
+          <t>[6.25, 8.19, 8.22]</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>[4.4, 2.6, 3.1]</t>
+          <t>[5.2, 3.6, 71.1]</t>
         </is>
       </c>
     </row>
@@ -5038,31 +5038,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>6.83</v>
+        <v>35.89</v>
       </c>
       <c r="E127" t="n">
-        <v>6.56</v>
+        <v>23.05</v>
       </c>
       <c r="F127" t="n">
-        <v>216.19</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>[10.79, 10.73, 8.25]</t>
+          <t>[7.46, 9.14, 7.03]</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>[2.6, 3.1, 4.4]</t>
+          <t>[3.6, 71.1, 3.7]</t>
         </is>
       </c>
     </row>
@@ -5074,31 +5074,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>4.3</v>
+        <v>36.19</v>
       </c>
       <c r="E128" t="n">
-        <v>3.6</v>
+        <v>22.33</v>
       </c>
       <c r="F128" t="n">
-        <v>102.88</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>[9.81, 7.47, 5.63]</t>
+          <t>[8.5, 6.58, 5.92]</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>[3.1, 4.4, 4.6]</t>
+          <t>[71.1, 3.7, 4.4]</t>
         </is>
       </c>
     </row>
@@ -5110,31 +5110,31 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1.67</v>
+        <v>3.28</v>
       </c>
       <c r="E129" t="n">
-        <v>1.46</v>
+        <v>3.18</v>
       </c>
       <c r="F129" t="n">
-        <v>27.05</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>[6.99, 5.24, 14.74]</t>
+          <t>[7.99, 7.29, 5.57]</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>[4.4, 4.6, 13.6]</t>
+          <t>[3.7, 4.4, 3.2]</t>
         </is>
       </c>
     </row>
@@ -5146,31 +5146,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1.46</v>
+        <v>2.82</v>
       </c>
       <c r="E130" t="n">
-        <v>1.18</v>
+        <v>2.75</v>
       </c>
       <c r="F130" t="n">
-        <v>15.38</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>[5.22, 14.12, 5.9]</t>
+          <t>[6.93, 5.31, 6.61]</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>[4.6, 13.6, 8.3]</t>
+          <t>[4.4, 3.2, 3.0]</t>
         </is>
       </c>
     </row>
@@ -5182,31 +5182,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1.43</v>
+        <v>3.27</v>
       </c>
       <c r="E131" t="n">
-        <v>1.23</v>
+        <v>3.17</v>
       </c>
       <c r="F131" t="n">
-        <v>16.05</v>
+        <v>101.46</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>[14.15, 6.06, 6.09]</t>
+          <t>[5.23, 6.52, 7.16]</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>[13.6, 8.3, 5.2]</t>
+          <t>[3.2, 3.0, 3.2]</t>
         </is>
       </c>
     </row>
@@ -5218,12 +5218,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[-0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, 0.0]</t>
+          <t>[-0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[0.0, -0.0, 0.0]</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5408,12 +5408,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 0.0]</t>
+          <t>[-0.0, 0.0, -0.0]</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, -0.0]</t>
+          <t>[0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5484,12 +5484,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>[0.0, -0.0, -0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>[-0.0, -0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>[-0.0, 0.0, 0.0]</t>
+          <t>[-0.0, -0.0, -0.0]</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5598,31 +5598,31 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>65.25</v>
+        <v>22.77</v>
       </c>
       <c r="E142" t="n">
-        <v>48.66</v>
+        <v>20.25</v>
       </c>
       <c r="F142" t="n">
-        <v>32.37</v>
+        <v>46.22</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>[95.8, 99.39, 102.87]</t>
+          <t>[13.29, 40.93, 16.84]</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>[76.1, 209.5, 86.7]</t>
+          <t>[23.4, 57.0, 51.4]</t>
         </is>
       </c>
     </row>
@@ -5634,31 +5634,31 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>67.63</v>
+        <v>62.87</v>
       </c>
       <c r="E143" t="n">
-        <v>49.6</v>
+        <v>52.48</v>
       </c>
       <c r="F143" t="n">
-        <v>28.77</v>
+        <v>76.81</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>[95.21, 98.28, 101.67]</t>
+          <t>[36.08, 15.57, 181.89]</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>[209.5, 86.7, 124.6]</t>
+          <t>[57.0, 51.4, 81.2]</t>
         </is>
       </c>
     </row>
@@ -5670,31 +5670,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>44.94</v>
+        <v>435.95</v>
       </c>
       <c r="E144" t="n">
-        <v>35.17</v>
+        <v>291.29</v>
       </c>
       <c r="F144" t="n">
-        <v>24.26</v>
+        <v>224.37</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>[113.9, 119.01, 124.18]</t>
+          <t>[13.66, 168.22, 901.2]</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>[86.7, 124.6, 196.9]</t>
+          <t>[51.4, 81.2, 152.1]</t>
         </is>
       </c>
     </row>
@@ -5706,31 +5706,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>72.56</v>
+        <v>308.57</v>
       </c>
       <c r="E145" t="n">
-        <v>62.46</v>
+        <v>190.79</v>
       </c>
       <c r="F145" t="n">
-        <v>142.28</v>
+        <v>133.34</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>[113.31, 117.86, 122.75]</t>
+          <t>[100.27, 685.86, 95.84]</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>[124.6, 196.9, 25.7]</t>
+          <t>[81.2, 152.1, 76.3]</t>
         </is>
       </c>
     </row>
@@ -5742,31 +5742,31 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>88.93000000000001</v>
+        <v>351.73</v>
       </c>
       <c r="E146" t="n">
-        <v>88.47</v>
+        <v>216.04</v>
       </c>
       <c r="F146" t="n">
-        <v>214.31</v>
+        <v>151.15</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>[119.77, 124.87, 130.01]</t>
+          <t>[760.64, 99.49, 54.92]</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>[196.9, 25.7, 40.9]</t>
+          <t>[152.1, 76.3, 71.3]</t>
         </is>
       </c>
     </row>
@@ -5778,31 +5778,31 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>111.86</v>
+        <v>76.92</v>
       </c>
       <c r="E147" t="n">
-        <v>111.41</v>
+        <v>49.64</v>
       </c>
       <c r="F147" t="n">
-        <v>401.03</v>
+        <v>65.02</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>[135.03, 141.24, 147.96]</t>
+          <t>[208.95, 59.71, 90.21]</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>[25.7, 40.9, 23.4]</t>
+          <t>[76.3, 71.3, 94.9]</t>
         </is>
       </c>
     </row>
@@ -5814,31 +5814,31 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>15.09</v>
+        <v>15.63</v>
       </c>
       <c r="E148" t="n">
-        <v>14.02</v>
+        <v>13.79</v>
       </c>
       <c r="F148" t="n">
-        <v>36.27</v>
+        <v>16.82</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>[19.44, 15.37, 44.43]</t>
+          <t>[95.47, 87.11, 122.01]</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>[40.9, 23.4, 57.0]</t>
+          <t>[71.3, 94.9, 112.6]</t>
         </is>
       </c>
     </row>
@@ -5850,31 +5850,31 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>22.77</v>
+        <v>16.21</v>
       </c>
       <c r="E149" t="n">
-        <v>20.25</v>
+        <v>13.96</v>
       </c>
       <c r="F149" t="n">
-        <v>46.22</v>
+        <v>11.06</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>[13.29, 40.93, 16.84]</t>
+          <t>[86.84, 120.84, 172.99]</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>[23.4, 57.0, 51.4]</t>
+          <t>[94.9, 112.6, 147.4]</t>
         </is>
       </c>
     </row>
@@ -5886,31 +5886,31 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>62.87</v>
+        <v>16.11</v>
       </c>
       <c r="E150" t="n">
-        <v>52.48</v>
+        <v>12.15</v>
       </c>
       <c r="F150" t="n">
-        <v>76.81</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>[36.08, 15.57, 181.89]</t>
+          <t>[121.41, 173.84, 31.69]</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>[57.0, 51.4, 81.2]</t>
+          <t>[112.6, 147.4, 30.5]</t>
         </is>
       </c>
     </row>
@@ -5922,31 +5922,31 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>435.95</v>
+        <v>16.57</v>
       </c>
       <c r="E151" t="n">
-        <v>291.29</v>
+        <v>13.14</v>
       </c>
       <c r="F151" t="n">
-        <v>224.37</v>
+        <v>25</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>[13.66, 168.22, 901.2]</t>
+          <t>[173.13, 31.5, 36.1]</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>[51.4, 81.2, 152.1]</t>
+          <t>[147.4, 30.5, 23.4]</t>
         </is>
       </c>
     </row>
@@ -5958,31 +5958,31 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>161.42</v>
+        <v>518.86</v>
       </c>
       <c r="E152" t="n">
-        <v>129.31</v>
+        <v>311.37</v>
       </c>
       <c r="F152" t="n">
-        <v>46.24</v>
+        <v>117.38</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>[210.4, 223.39, 236.27]</t>
+          <t>[219.94, 228.73, 1167.27]</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>[129.91, 180.21, 500.52]</t>
+          <t>[189.78, 234.52, 269.1]</t>
         </is>
       </c>
     </row>
@@ -5994,31 +5994,31 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>166.94</v>
+        <v>1024.23</v>
       </c>
       <c r="E153" t="n">
-        <v>114.73</v>
+        <v>812.46</v>
       </c>
       <c r="F153" t="n">
-        <v>29.41</v>
+        <v>341.76</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>[203.94, 214.4, 226.17]</t>
+          <t>[236.3, 1185.99, 1740.8]</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>[180.21, 500.52, 191.82]</t>
+          <t>[234.52, 269.1, 222.1]</t>
         </is>
       </c>
     </row>
@@ -6030,31 +6030,31 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>176.06</v>
+        <v>1032.34</v>
       </c>
       <c r="E154" t="n">
-        <v>123.48</v>
+        <v>884.92</v>
       </c>
       <c r="F154" t="n">
-        <v>33.43</v>
+        <v>383.07</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>[200.57, 210.62, 220.81]</t>
+          <t>[1187.17, 1740.95, 393.24]</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>[500.52, 191.82, 169.13]</t>
+          <t>[269.1, 222.1, 175.4]</t>
         </is>
       </c>
     </row>
@@ -6066,31 +6066,31 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>190.72</v>
+        <v>1682.43</v>
       </c>
       <c r="E155" t="n">
-        <v>160.79</v>
+        <v>1119.07</v>
       </c>
       <c r="F155" t="n">
-        <v>50.42</v>
+        <v>529.64</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>[261.48, 277.75, 295.62]</t>
+          <t>[3111.91, 534.47, 22.09]</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>[191.82, 169.13, 599.72]</t>
+          <t>[222.1, 175.4, 130.43]</t>
         </is>
       </c>
     </row>
@@ -6102,31 +6102,31 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>205.59</v>
+        <v>983.3</v>
       </c>
       <c r="E156" t="n">
-        <v>176.91</v>
+        <v>610.66</v>
       </c>
       <c r="F156" t="n">
-        <v>57.86</v>
+        <v>356.27</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>[259.66, 275.43, 291.59]</t>
+          <t>[1875.45, 34.53, 102.28]</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>[169.13, 599.72, 175.68]</t>
+          <t>[175.4, 130.43, 138.3]</t>
         </is>
       </c>
     </row>
@@ -6138,31 +6138,31 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>212.94</v>
+        <v>415.78</v>
       </c>
       <c r="E157" t="n">
-        <v>177.56</v>
+        <v>256.65</v>
       </c>
       <c r="F157" t="n">
-        <v>53.61</v>
+        <v>127.69</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>[255.93, 269.69, 284.68]</t>
+          <t>[102.93, 115.11, 927.6]</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>[599.72, 175.68, 189.78]</t>
+          <t>[130.43, 138.3, 208.34]</t>
         </is>
       </c>
     </row>
@@ -6174,31 +6174,31 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>49.74</v>
+        <v>423.5</v>
       </c>
       <c r="E158" t="n">
-        <v>42.3</v>
+        <v>284.63</v>
       </c>
       <c r="F158" t="n">
-        <v>23.03</v>
+        <v>143.26</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>[107.57, 242.13, 240.96]</t>
+          <t>[103.14, 935.24, 257.44]</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>[175.68, 189.78, 234.52]</t>
+          <t>[138.3, 208.34, 165.61]</t>
         </is>
       </c>
     </row>
@@ -6210,31 +6210,31 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>518.86</v>
+        <v>435.69</v>
       </c>
       <c r="E159" t="n">
-        <v>311.37</v>
+        <v>322.99</v>
       </c>
       <c r="F159" t="n">
-        <v>117.38</v>
+        <v>163.23</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>[219.94, 228.73, 1167.27]</t>
+          <t>[944.18, 261.51, 311.86]</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>[189.78, 234.52, 269.1]</t>
+          <t>[208.34, 165.61, 174.63]</t>
         </is>
       </c>
     </row>
@@ -6246,31 +6246,31 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1024.23</v>
+        <v>285.77</v>
       </c>
       <c r="E160" t="n">
-        <v>812.46</v>
+        <v>204.1</v>
       </c>
       <c r="F160" t="n">
-        <v>341.76</v>
+        <v>51.99</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>[236.3, 1185.99, 1740.8]</t>
+          <t>[213.28, 252.83, 1076.79]</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>[234.52, 269.1, 222.1]</t>
+          <t>[165.61, 174.63, 590.36]</t>
         </is>
       </c>
     </row>
@@ -6282,31 +6282,31 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1032.34</v>
+        <v>325.82</v>
       </c>
       <c r="E161" t="n">
-        <v>884.92</v>
+        <v>224.32</v>
       </c>
       <c r="F161" t="n">
-        <v>383.07</v>
+        <v>53.48</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>[1187.17, 1740.95, 393.24]</t>
+          <t>[274.82, 1145.46, 213.17]</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>[269.1, 222.1, 175.4]</t>
+          <t>[174.63, 590.36, 195.49]</t>
         </is>
       </c>
     </row>
@@ -6318,31 +6318,33 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1.59</v>
+        <v>0.35</v>
       </c>
       <c r="E162" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F162" t="n">
-        <v>88.69</v>
+        <v>0.29</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>[0.19, 0.17, 0.15]</t>
+          <t>[0.04, 2.09, 0.01]</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>[2.2, 1.9, 0.9]</t>
+          <t>[0.4, 1.6, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6354,19 +6356,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1.02</v>
+        <v>0.22</v>
       </c>
       <c r="E163" t="n">
-        <v>0.83</v>
+        <v>0.15</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -6375,12 +6377,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>[0.27, 0.25, 0.22]</t>
+          <t>[1.24, 0.01, 0.08]</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>[1.9, 0.9, 0.0]</t>
+          <t>[1.6, 0.0, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6392,19 +6394,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.59</v>
+        <v>1.04</v>
       </c>
       <c r="E164" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -6413,12 +6415,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>[0.36, 0.33, 0.3]</t>
+          <t>[0.01, 0.08, 1.8]</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>[0.9, 0.0, 1.1]</t>
+          <t>[0.0, 0.0, 3.6]</t>
         </is>
       </c>
     </row>
@@ -6430,19 +6432,19 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.52</v>
+        <v>4.4</v>
       </c>
       <c r="E165" t="n">
-        <v>0.49</v>
+        <v>3.82</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -6451,12 +6453,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>[0.39, 0.36, 0.33]</t>
+          <t>[2.36, 10.5, 0.0]</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>[0.0, 1.1, 0.0]</t>
+          <t>[0.0, 3.6, 2.2]</t>
         </is>
       </c>
     </row>
@@ -6468,33 +6470,31 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1.61</v>
+        <v>6120.31</v>
       </c>
       <c r="E166" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>3535</v>
+      </c>
+      <c r="F166" t="n">
+        <v>98221.14999999999</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>[0.04, 0.03, 0.03]</t>
+          <t>[10604.29, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>[1.1, 0.0, 2.6]</t>
+          <t>[3.6, 2.2, 2.1]</t>
         </is>
       </c>
     </row>
@@ -6506,33 +6506,31 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1.49</v>
+        <v>1.82</v>
       </c>
       <c r="E167" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>1.76</v>
+      </c>
+      <c r="F167" t="n">
+        <v>97.92</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>[0.05, 0.05, 0.04]</t>
+          <t>[0.11, 0.0, 0.01]</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>[0.0, 2.6, 0.4]</t>
+          <t>[2.2, 2.1, 1.1]</t>
         </is>
       </c>
     </row>
@@ -6544,31 +6542,33 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="E168" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F168" t="n">
-        <v>94.06999999999999</v>
+        <v>1.06</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>[0.06, 0.08, 3.25]</t>
+          <t>[0.0, 0.01, -0.0]</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>[2.6, 0.4, 1.6]</t>
+          <t>[2.1, 1.1, 0.0]</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6580,19 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.35</v>
+        <v>0.96</v>
       </c>
       <c r="E169" t="n">
-        <v>0.29</v>
+        <v>0.78</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -6601,12 +6601,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>[0.04, 2.09, 0.01]</t>
+          <t>[0.02, -0.0, 0.03]</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>[0.4, 1.6, 0.0]</t>
+          <t>[1.1, 0.0, 1.3]</t>
         </is>
       </c>
     </row>
@@ -6618,19 +6618,19 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.22</v>
+        <v>1.46</v>
       </c>
       <c r="E170" t="n">
-        <v>0.15</v>
+        <v>1.15</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>[1.24, 0.01, 0.08]</t>
+          <t>[-0.0, 0.04, 0.0]</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>[1.6, 0.0, 0.0]</t>
+          <t>[0.0, 1.3, 2.2]</t>
         </is>
       </c>
     </row>
@@ -6656,33 +6656,31 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1.04</v>
+        <v>2.05</v>
       </c>
       <c r="E171" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>1.98</v>
+      </c>
+      <c r="F171" t="n">
+        <v>97.44</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>[0.01, 0.08, 1.8]</t>
+          <t>[0.05, 0.0, 0.1]</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>[0.0, 0.0, 3.6]</t>
+          <t>[1.3, 2.2, 2.6]</t>
         </is>
       </c>
     </row>
@@ -6694,31 +6692,31 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>180.62</v>
+        <v>59.69</v>
       </c>
       <c r="E172" t="n">
-        <v>120.92</v>
+        <v>58.34</v>
       </c>
       <c r="F172" t="n">
-        <v>8.41</v>
+        <v>3.52</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>[1680.54, 1724.46, 1440.77]</t>
+          <t>[1682.3, 1484.25, 1724.52]</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>[1638.33, 1414.67, 1451.52]</t>
+          <t>[1617.42, 1524.98, 1793.94]</t>
         </is>
       </c>
     </row>
@@ -6730,31 +6728,31 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>208.4</v>
+        <v>217.3</v>
       </c>
       <c r="E173" t="n">
-        <v>173.16</v>
+        <v>162.95</v>
       </c>
       <c r="F173" t="n">
-        <v>11.12</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>[1710.88, 1433.76, 1631.89]</t>
+          <t>[1477.53, 1718.15, 2101.3]</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>[1414.67, 1451.52, 1837.4]</t>
+          <t>[1524.98, 1793.94, 1735.7]</t>
         </is>
       </c>
     </row>
@@ -6766,31 +6764,31 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>149.5</v>
+        <v>580.58</v>
       </c>
       <c r="E174" t="n">
-        <v>113.63</v>
+        <v>457.24</v>
       </c>
       <c r="F174" t="n">
-        <v>6.51</v>
+        <v>27.09</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>[1396.87, 1586.81, 1648.56]</t>
+          <t>[1722.54, 2102.43, 2595.76]</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>[1451.52, 1837.4, 1684.2]</t>
+          <t>[1793.94, 1735.7, 1662.16]</t>
         </is>
       </c>
     </row>
@@ -6802,31 +6800,31 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>155.99</v>
+        <v>615.72</v>
       </c>
       <c r="E175" t="n">
-        <v>124.14</v>
+        <v>543.86</v>
       </c>
       <c r="F175" t="n">
-        <v>7.06</v>
+        <v>34.53</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>[1581.27, 1643.82, 1487.28]</t>
+          <t>[2117.6, 2611.52, 1527.38]</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>[1837.4, 1684.2, 1563.17]</t>
+          <t>[1735.7, 1662.16, 1227.05]</t>
         </is>
       </c>
     </row>
@@ -6838,31 +6836,31 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>109.13</v>
+        <v>707.49</v>
       </c>
       <c r="E176" t="n">
-        <v>84.05</v>
+        <v>648.02</v>
       </c>
       <c r="F176" t="n">
-        <v>5.46</v>
+        <v>43.57</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>[1665.82, 1509.82, 1701.28]</t>
+          <t>[2582.59, 1483.38, 2176.23]</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>[1684.2, 1563.17, 1520.87]</t>
+          <t>[1662.16, 1227.05, 1408.94]</t>
         </is>
       </c>
     </row>
@@ -6874,31 +6872,31 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>119.35</v>
+        <v>491.73</v>
       </c>
       <c r="E177" t="n">
-        <v>103.74</v>
+        <v>444.35</v>
       </c>
       <c r="F177" t="n">
-        <v>6.69</v>
+        <v>30.17</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>[1512.8, 1706.84, 1692.31]</t>
+          <t>[1456.46, 2139.3, 1494.7]</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>[1563.17, 1520.87, 1617.42]</t>
+          <t>[1227.05, 1408.94, 1867.97]</t>
         </is>
       </c>
     </row>
@@ -6910,31 +6908,31 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>115.55</v>
+        <v>459.96</v>
       </c>
       <c r="E178" t="n">
-        <v>96.09</v>
+        <v>412.57</v>
       </c>
       <c r="F178" t="n">
-        <v>6.22</v>
+        <v>26.77</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>[1704.21, 1691.51, 1494.13]</t>
+          <t>[2080.0, 1475.49, 1668.38]</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>[1520.87, 1617.42, 1524.98]</t>
+          <t>[1408.94, 1867.97, 1494.22]</t>
         </is>
       </c>
     </row>
@@ -6946,31 +6944,31 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>59.69</v>
+        <v>267.68</v>
       </c>
       <c r="E179" t="n">
-        <v>58.34</v>
+        <v>229.88</v>
       </c>
       <c r="F179" t="n">
-        <v>3.52</v>
+        <v>13.46</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>[1682.3, 1484.25, 1724.52]</t>
+          <t>[1444.14, 1627.54, 1645.37]</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>[1617.42, 1524.98, 1793.94]</t>
+          <t>[1867.97, 1494.22, 1512.88]</t>
         </is>
       </c>
     </row>
@@ -6982,31 +6980,31 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>217.3</v>
+        <v>132.81</v>
       </c>
       <c r="E180" t="n">
-        <v>162.95</v>
+        <v>123.66</v>
       </c>
       <c r="F180" t="n">
-        <v>9.470000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>[1477.53, 1718.15, 2101.3]</t>
+          <t>[1651.8, 1671.12, 1531.7]</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>[1524.98, 1793.94, 1735.7]</t>
+          <t>[1494.22, 1512.88, 1586.88]</t>
         </is>
       </c>
     </row>
@@ -7018,31 +7016,31 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>580.58</v>
+        <v>120.71</v>
       </c>
       <c r="E181" t="n">
-        <v>457.24</v>
+        <v>114.84</v>
       </c>
       <c r="F181" t="n">
-        <v>27.09</v>
+        <v>7.49</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>[1722.54, 2102.43, 2595.76]</t>
+          <t>[1663.11, 1523.44, 1660.02]</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>[1793.94, 1735.7, 1662.16]</t>
+          <t>[1512.88, 1586.88, 1529.18]</t>
         </is>
       </c>
     </row>
@@ -7054,31 +7052,31 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>547.12</v>
+        <v>1412.4</v>
       </c>
       <c r="E182" t="n">
-        <v>484.94</v>
+        <v>1156.97</v>
       </c>
       <c r="F182" t="n">
-        <v>29.21</v>
+        <v>83.37</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>[2319.53, 2393.36, 1518.8]</t>
+          <t>[2027.61, 1382.35, 3845.72]</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>[1714.02, 1676.54, 1386.32]</t>
+          <t>[1183.77, 1023.24, 1577.77]</t>
         </is>
       </c>
     </row>
@@ -7090,31 +7088,31 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>346.47</v>
+        <v>1390.69</v>
       </c>
       <c r="E183" t="n">
-        <v>260.46</v>
+        <v>1168.83</v>
       </c>
       <c r="F183" t="n">
-        <v>16.08</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>[2243.9, 1366.83, 1691.89]</t>
+          <t>[1327.48, 3718.46, 2304.78]</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>[1676.54, 1386.32, 1497.36]</t>
+          <t>[1023.24, 1577.77, 1243.23]</t>
         </is>
       </c>
     </row>
@@ -7126,31 +7124,31 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>229.5</v>
+        <v>1428.7</v>
       </c>
       <c r="E184" t="n">
-        <v>175.12</v>
+        <v>1315.07</v>
       </c>
       <c r="F184" t="n">
-        <v>13.81</v>
+        <v>85.38</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>[1363.15, 1623.21, 1577.15]</t>
+          <t>[3673.7, 2269.57, 2843.03]</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>[1386.32, 1497.36, 1200.8]</t>
+          <t>[1577.77, 1243.23, 2020.1]</t>
         </is>
       </c>
     </row>
@@ -7162,31 +7160,31 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>979.78</v>
+        <v>619.5700000000001</v>
       </c>
       <c r="E185" t="n">
-        <v>701.4299999999999</v>
+        <v>536.6900000000001</v>
       </c>
       <c r="F185" t="n">
-        <v>40.47</v>
+        <v>35.97</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>[1598.01, 1545.95, 271.05]</t>
+          <t>[2115.52, 2632.45, 1814.58]</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>[1497.36, 1200.8, 1929.55]</t>
+          <t>[1243.23, 2020.1, 1689.17]</t>
         </is>
       </c>
     </row>
@@ -7198,31 +7196,31 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1728</v>
+        <v>280.3</v>
       </c>
       <c r="E186" t="n">
-        <v>1499.67</v>
+        <v>177.37</v>
       </c>
       <c r="F186" t="n">
-        <v>84.58</v>
+        <v>8.93</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>[1581.0, 277.03, 4273.95]</t>
+          <t>[2504.4, 1710.44, 1695.39]</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>[1200.8, 1929.55, 1807.66]</t>
+          <t>[2020.1, 1689.17, 1721.94]</t>
         </is>
       </c>
     </row>
@@ -7234,31 +7232,31 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1672.58</v>
+        <v>311.87</v>
       </c>
       <c r="E187" t="n">
-        <v>1514.73</v>
+        <v>198.22</v>
       </c>
       <c r="F187" t="n">
-        <v>87.5</v>
+        <v>11.76</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>[265.26, 4106.63, 1764.71]</t>
+          <t>[1737.87, 1730.0, 1146.09]</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>[1929.55, 1807.66, 1183.77]</t>
+          <t>[1689.17, 1721.94, 1684.0]</t>
         </is>
       </c>
     </row>
@@ -7270,31 +7268,31 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1830.52</v>
+        <v>462.2</v>
       </c>
       <c r="E188" t="n">
-        <v>1484.14</v>
+        <v>384.13</v>
       </c>
       <c r="F188" t="n">
-        <v>98.63</v>
+        <v>21.77</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>[4775.83, 2191.3, 1499.95]</t>
+          <t>[1701.26, 1124.73, 1280.32]</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>[1807.66, 1183.77, 1023.24]</t>
+          <t>[1721.94, 1684.0, 1852.75]</t>
         </is>
       </c>
     </row>
@@ -7306,31 +7304,31 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1412.4</v>
+        <v>496.65</v>
       </c>
       <c r="E189" t="n">
-        <v>1156.97</v>
+        <v>489.12</v>
       </c>
       <c r="F189" t="n">
-        <v>83.37</v>
+        <v>28.47</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>[2027.61, 1382.35, 3845.72]</t>
+          <t>[1139.41, 1297.44, 1223.61]</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>[1183.77, 1023.24, 1577.77]</t>
+          <t>[1684.0, 1852.75, 1591.07]</t>
         </is>
       </c>
     </row>
@@ -7342,31 +7340,31 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1390.69</v>
+        <v>729.88</v>
       </c>
       <c r="E190" t="n">
-        <v>1168.83</v>
+        <v>647.16</v>
       </c>
       <c r="F190" t="n">
-        <v>83.59999999999999</v>
+        <v>41.59</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>[1327.48, 3718.46, 2304.78]</t>
+          <t>[1345.09, 1269.46, 329.31]</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>[1023.24, 1577.77, 1243.23]</t>
+          <t>[1852.75, 1591.07, 1441.53]</t>
         </is>
       </c>
     </row>
@@ -7378,31 +7376,31 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1428.7</v>
+        <v>701.13</v>
       </c>
       <c r="E191" t="n">
-        <v>1315.07</v>
+        <v>603.23</v>
       </c>
       <c r="F191" t="n">
-        <v>85.38</v>
+        <v>36.29</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>[3673.7, 2269.57, 2843.03]</t>
+          <t>[1326.32, 344.08, 3227.54]</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>[1577.77, 1243.23, 2020.1]</t>
+          <t>[1591.07, 1441.53, 2780.05]</t>
         </is>
       </c>
     </row>
@@ -7414,31 +7412,31 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="E192" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="F192" t="n">
-        <v>45.45</v>
+        <v>71.25</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>[0.97, 1.45, 0.97]</t>
+          <t>[0.45, 0.83, 0.52]</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>[0.7, 2.3, 2.5]</t>
+          <t>[2.2, 0.5, 1.6]</t>
         </is>
       </c>
     </row>
@@ -7450,31 +7448,31 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1.09</v>
+        <v>3.06</v>
       </c>
       <c r="E193" t="n">
-        <v>1</v>
+        <v>2.22</v>
       </c>
       <c r="F193" t="n">
-        <v>58.67</v>
+        <v>83.38</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>[1.41, 0.92, 1.22]</t>
+          <t>[1.01, 0.64, 0.71]</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>[2.3, 2.5, 0.7]</t>
+          <t>[0.5, 1.6, 5.9]</t>
         </is>
       </c>
     </row>
@@ -7486,31 +7484,31 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.95</v>
+        <v>4.3</v>
       </c>
       <c r="E194" t="n">
-        <v>0.78</v>
+        <v>3.81</v>
       </c>
       <c r="F194" t="n">
-        <v>55.19</v>
+        <v>80.37</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>[0.97, 1.27, 1.24]</t>
+          <t>[0.63, 0.69, 0.46]</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>[2.5, 0.7, 1.0]</t>
+          <t>[1.6, 5.9, 5.7]</t>
         </is>
       </c>
     </row>
@@ -7522,33 +7520,31 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.9</v>
+        <v>4.27</v>
       </c>
       <c r="E195" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>3.57</v>
+      </c>
+      <c r="F195" t="n">
+        <v>80.89</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>[1.43, 1.45, 1.3]</t>
+          <t>[0.68, 0.47, 0.15]</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>[0.7, 1.0, 0.0]</t>
+          <t>[5.9, 5.7, 0.4]</t>
         </is>
       </c>
     </row>
@@ -7560,33 +7556,31 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>2.18</v>
+        <v>3.01</v>
       </c>
       <c r="E196" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>2.04</v>
+      </c>
+      <c r="F196" t="n">
+        <v>70.56999999999999</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>[1.61, 1.44, 1.65]</t>
+          <t>[0.55, 0.2, 0.33]</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>[1.0, 0.0, 5.1]</t>
+          <t>[5.7, 0.4, 1.1]</t>
         </is>
       </c>
     </row>
@@ -7598,33 +7592,31 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>2.48</v>
+        <v>0.82</v>
       </c>
       <c r="E197" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.7</v>
+      </c>
+      <c r="F197" t="n">
+        <v>58.72</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>[1.26, 1.44, 0.36]</t>
+          <t>[0.22, 0.4, 0.58]</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>[0.0, 5.1, 2.2]</t>
+          <t>[0.4, 1.1, 1.8]</t>
         </is>
       </c>
     </row>
@@ -7636,31 +7628,31 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1.87</v>
+        <v>0.82</v>
       </c>
       <c r="E198" t="n">
-        <v>1.6</v>
+        <v>0.67</v>
       </c>
       <c r="F198" t="n">
-        <v>66.17</v>
+        <v>49.33</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>[2.39, 0.45, 0.83]</t>
+          <t>[0.37, 0.58, 0.46]</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>[5.1, 2.2, 0.5]</t>
+          <t>[1.1, 1.8, 0.4]</t>
         </is>
       </c>
     </row>
@@ -7672,31 +7664,31 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1.2</v>
+        <v>0.66</v>
       </c>
       <c r="E199" t="n">
-        <v>1.06</v>
+        <v>0.46</v>
       </c>
       <c r="F199" t="n">
-        <v>71.25</v>
+        <v>38.65</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>[0.45, 0.83, 0.52]</t>
+          <t>[0.68, 0.55, 0.58]</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>[2.2, 0.5, 1.6]</t>
+          <t>[1.8, 0.4, 0.7]</t>
         </is>
       </c>
     </row>
@@ -7708,31 +7700,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>3.06</v>
+        <v>0.15</v>
       </c>
       <c r="E200" t="n">
-        <v>2.22</v>
+        <v>0.15</v>
       </c>
       <c r="F200" t="n">
-        <v>83.38</v>
+        <v>46.8</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>[1.01, 0.64, 0.71]</t>
+          <t>[0.56, 0.59, 0.03]</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>[0.5, 1.6, 5.9]</t>
+          <t>[0.4, 0.7, 0.2]</t>
         </is>
       </c>
     </row>
@@ -7744,31 +7736,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>4.3</v>
+        <v>0.17</v>
       </c>
       <c r="E201" t="n">
-        <v>3.81</v>
+        <v>0.17</v>
       </c>
       <c r="F201" t="n">
-        <v>80.37</v>
+        <v>39.38</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>[0.63, 0.69, 0.46]</t>
+          <t>[0.58, 0.03, 1.19]</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>[1.6, 5.9, 5.7]</t>
+          <t>[0.7, 0.2, 1.4]</t>
         </is>
       </c>
     </row>
